--- a/output/pdf_financials_xlsx/CCMI.xlsx
+++ b/output/pdf_financials_xlsx/CCMI.xlsx
@@ -6303,13 +6303,13 @@
         <v>-0.013</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.0035</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.037</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.624003</v>
       </c>
       <c r="L103" s="1" t="inlineStr">
         <is>
@@ -6504,13 +6504,13 @@
         <v>-0.187443</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.061296</v>
+        <v>-0.06479600000000001</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.029538</v>
+        <v>-0.066538</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.17116</v>
+        <v>-0.452843</v>
       </c>
       <c r="L106" s="1" t="inlineStr">
         <is>
@@ -9388,7 +9388,11 @@
           <t>Prepaids and deposits 9</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -11910,7 +11914,11 @@
           <t>Prepaids and deposits 8</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -23116,7 +23124,11 @@
           <t>Prepaids and deposits 9</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -25388,7 +25400,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CCMI.xlsx
+++ b/output/pdf_financials_xlsx/CCMI.xlsx
@@ -1037,13 +1037,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000163</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000343</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.026433</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014214</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007312</v>
       </c>
     </row>
     <row r="13">
@@ -2040,13 +2040,13 @@
         <v>-0.465492</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.68167</v>
+        <v>-0.681833</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.914855</v>
+        <v>-2.914512</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-5.28417</v>
+        <v>-5.257737</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.05433</v>
+        <v>0.06854399999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.786588</v>
       </c>
     </row>
     <row r="28">
@@ -2156,13 +2156,13 @@
         <v>-0.465492</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.68167</v>
+        <v>-0.681833</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.914855</v>
+        <v>-2.914512</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-5.28417</v>
+        <v>-5.257737</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.05433</v>
+        <v>0.06854399999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.786588</v>
       </c>
     </row>
     <row r="30">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>11.04948779431235</v>
+        <v>13.94029249720865</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-19.54053288379524</v>
+        <v>-19.36056012092043</v>
       </c>
     </row>
     <row r="31">
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.085651</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.097209</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.148372</v>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.085651</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.097209</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.148372</v>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.085651</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.431531</v>
+        <v>0.334322</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.012893</v>
@@ -22064,7 +22064,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -34024,7 +34024,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -34606,7 +34606,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -39976,7 +39976,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -42362,7 +42362,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -45138,7 +45138,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -47920,7 +47920,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -48492,7 +48492,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -52428,7 +52428,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">

--- a/output/pdf_financials_xlsx/CCMI.xlsx
+++ b/output/pdf_financials_xlsx/CCMI.xlsx
@@ -7433,19 +7433,19 @@
         <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>0.25525</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>0.67325</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>0.406975</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>0.738866</v>
       </c>
       <c r="K120" s="3" t="n">
         <v>0</v>
@@ -25788,7 +25788,11 @@
           <t>Issue of common shares, net of issue costs 9</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -27078,7 +27082,11 @@
           <t>Issue of common shares, net of issue cost</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CCMI.xlsx
+++ b/output/pdf_financials_xlsx/CCMI.xlsx
@@ -1263,7 +1263,7 @@
         <v>-2.914855</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-5.28417</v>
+        <v>-5.340698</v>
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.05433</v>
+        <v>-0.022267</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-1.094103</v>
       </c>
     </row>
     <row r="17">
@@ -1324,7 +1324,7 @@
         <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>0.056528</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1336,10 +1336,10 @@
         <v>-0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>0.076597</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>0.300203</v>
       </c>
     </row>
     <row r="18">
@@ -2046,7 +2046,7 @@
         <v>-2.914512</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-5.257737</v>
+        <v>-5.314265</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.06854399999999999</v>
+        <v>-0.008052999999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.786588</v>
+        <v>-1.086791</v>
       </c>
     </row>
     <row r="28">
@@ -2162,7 +2162,7 @@
         <v>-2.914512</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-5.257737</v>
+        <v>-5.314265</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.06854399999999999</v>
+        <v>-0.008052999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.786588</v>
+        <v>-1.086791</v>
       </c>
     </row>
     <row r="30">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>13.94029249720865</v>
+        <v>-1.637797261321505</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-19.36056012092043</v>
+        <v>-26.74955948269645</v>
       </c>
     </row>
     <row r="31">
@@ -2306,7 +2306,7 @@
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.058438428834583</v>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-343.9933533929133</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-27.43827592100561</v>
       </c>
     </row>
     <row r="32">
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>0.141508</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>0.141508</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
         <v>0.376579</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.249346</v>
+        <v>0.107838</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.627773</v>
@@ -4145,16 +4145,16 @@
         <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.727251</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>1.281062</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>1.430811</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>1.667184</v>
       </c>
     </row>
     <row r="65">
@@ -6169,10 +6169,10 @@
         <v>0</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.007541</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.020132</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0</v>
@@ -6504,10 +6504,10 @@
         <v>-0.187443</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.06479600000000001</v>
+        <v>-0.057255</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.066538</v>
+        <v>-0.08667</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>-0.452843</v>
@@ -6778,7 +6778,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.008482999999999999</v>
       </c>
       <c r="L110" s="1" t="inlineStr">
         <is>
@@ -22646,7 +22646,11 @@
           <t>Acretion 18</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -25306,7 +25310,11 @@
           <t>GST/HST receivable 8</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -31602,7 +31610,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -34804,7 +34816,11 @@
           <t>Deferred income tax recovery 14, 20</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -36230,7 +36246,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -48788,7 +48808,11 @@
           <t>Corporate income tax recovery 13</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
